--- a/public/tableau_synthese_2026f.xlsx
+++ b/public/tableau_synthese_2026f.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{485414AE-D03C-41BF-903C-C22D79564023}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4358CA0F-72CE-499A-B299-9DB26FA2C0A1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="44">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -121,9 +121,6 @@
     <t>SESSION 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Conception et développement du site internet Cabinet médical </t>
-  </si>
-  <si>
     <t>NOM et prénom :HAROUN Djihane</t>
   </si>
   <si>
@@ -137,9 +134,6 @@
   </si>
   <si>
     <t>Formation Certification en MOOC SecNumacadémie,Certifications CNIL – RGPD</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Elaboration d'une veille technologique sur L'IA dans le monde du travail ,Cybersécurité des objets connectés (IoT)</t>
   </si>
   <si>
     <r>
@@ -168,12 +162,6 @@
     <t xml:space="preserve">Devloppement du site auto-ecole wn MVC-POO PHP Mysql HTml CSS avec la gestion du projet </t>
   </si>
   <si>
-    <t>Conception et devloppement d'une application Android Enquete de satisfaction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developpement du site marchant </t>
-  </si>
-  <si>
     <t>Création d’une page utilisateur pour téléchargement de guides 
 (PHP, Symfony, Twig, formulaire interactif, envoi automatique 
 de mails avec PDF)</t>
@@ -255,6 +243,12 @@
   </si>
   <si>
     <t>Intégration de nouvelles fonctionnalités avec personnalisation et gestion multilingue du site internet de l’entreprise.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Elaboration d'une veille technologique sur L'IA dans le monde du travail</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -842,87 +836,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -948,6 +861,87 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1270,56 +1264,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29" t="s">
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="29"/>
+      <c r="H1" s="39"/>
     </row>
     <row r="2" spans="1:43" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
     </row>
     <row r="3" spans="1:43" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="37"/>
-      <c r="H3" s="38"/>
+      <c r="A3" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="47"/>
+      <c r="H3" s="48"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="35"/>
+      <c r="A4" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="45"/>
       <c r="F4" s="6" t="s">
         <v>2</v>
       </c>
@@ -1331,22 +1325,22 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="49" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="51"/>
+      <c r="A5" s="59" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="60"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="61"/>
     </row>
     <row r="6" spans="1:43" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="39" t="s">
+      <c r="A6" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="47" t="s">
+      <c r="B6" s="57" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="9" t="s">
@@ -1369,8 +1363,8 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="232.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="39"/>
-      <c r="B7" s="48"/>
+      <c r="A7" s="49"/>
+      <c r="B7" s="58"/>
       <c r="C7" s="18" t="s">
         <v>13</v>
       </c>
@@ -1426,16 +1420,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="40" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" s="41"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="42"/>
+      <c r="A8" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="51"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="52"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1572,7 +1566,7 @@
     </row>
     <row r="11" spans="1:43" s="2" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B11" s="14">
         <v>45942</v>
@@ -1621,7 +1615,7 @@
     </row>
     <row r="12" spans="1:43" s="2" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B12" s="14">
         <v>45953</v>
@@ -1670,7 +1664,7 @@
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="B13" s="14">
         <v>45352</v>
@@ -1717,9 +1711,9 @@
       <c r="AP13"/>
       <c r="AQ13"/>
     </row>
-    <row r="14" spans="1:43" s="2" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:43" s="2" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B14" s="17">
         <v>45597</v>
@@ -1766,10 +1760,8 @@
       <c r="AP14"/>
       <c r="AQ14"/>
     </row>
-    <row r="15" spans="1:43" s="2" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>22</v>
-      </c>
+    <row r="15" spans="1:43" s="2" customFormat="1" ht="6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3"/>
       <c r="B15" s="17">
         <v>45992</v>
       </c>
@@ -1817,7 +1809,7 @@
     </row>
     <row r="16" spans="1:43" s="2" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B16" s="17">
         <v>45931</v>
@@ -1864,13 +1856,9 @@
       <c r="AP16"/>
       <c r="AQ16"/>
     </row>
-    <row r="17" spans="1:43" s="2" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" s="17">
-        <v>46054</v>
-      </c>
+    <row r="17" spans="1:43" s="2" customFormat="1" ht="1.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3"/>
+      <c r="B17" s="17"/>
       <c r="C17" s="4"/>
       <c r="D17" s="12"/>
       <c r="E17" s="4"/>
@@ -1913,13 +1901,11 @@
       <c r="AP17"/>
       <c r="AQ17"/>
     </row>
-    <row r="18" spans="1:43" s="2" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:43" s="2" customFormat="1" ht="1.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18" s="17">
-        <v>46054</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="B18" s="17"/>
       <c r="C18" s="4"/>
       <c r="D18" s="12"/>
       <c r="E18" s="4"/>
@@ -1963,16 +1949,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="43" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19" s="44"/>
-      <c r="C19" s="44"/>
-      <c r="D19" s="44"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="45"/>
+      <c r="A19" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="54"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="55"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -2010,16 +1996,16 @@
       <c r="AQ19"/>
     </row>
     <row r="20" spans="1:43" s="2" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="B20" s="25"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="25"/>
+      <c r="A20" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="35"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="35"/>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
@@ -2058,10 +2044,10 @@
     </row>
     <row r="21" spans="1:43" s="2" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="22" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C21" s="16"/>
       <c r="D21" s="4"/>
@@ -2107,10 +2093,10 @@
     </row>
     <row r="22" spans="1:43" s="2" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="23" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C22" s="16"/>
       <c r="D22" s="20"/>
@@ -2156,10 +2142,10 @@
     </row>
     <row r="23" spans="1:43" s="2" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C23" s="16"/>
       <c r="D23" s="16"/>
@@ -2204,16 +2190,16 @@
       <c r="AQ23"/>
     </row>
     <row r="24" spans="1:43" s="2" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="43" t="s">
-        <v>37</v>
-      </c>
-      <c r="B24" s="44"/>
-      <c r="C24" s="44"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="44"/>
-      <c r="F24" s="44"/>
-      <c r="G24" s="44"/>
-      <c r="H24" s="45"/>
+      <c r="A24" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="54"/>
+      <c r="C24" s="54"/>
+      <c r="D24" s="56"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="54"/>
+      <c r="H24" s="55"/>
       <c r="I24"/>
       <c r="J24"/>
       <c r="K24"/>
@@ -2251,16 +2237,16 @@
       <c r="AQ24"/>
     </row>
     <row r="25" spans="1:43" s="2" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="27"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="27"/>
-      <c r="H25" s="28"/>
+      <c r="A25" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="37"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="37"/>
+      <c r="H25" s="38"/>
       <c r="I25"/>
       <c r="J25"/>
       <c r="K25"/>
@@ -2298,18 +2284,18 @@
       <c r="AQ25"/>
     </row>
     <row r="26" spans="1:43" s="2" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="52" t="s">
-        <v>45</v>
-      </c>
-      <c r="B26" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="C26" s="53"/>
-      <c r="D26" s="54"/>
-      <c r="E26" s="55"/>
-      <c r="F26" s="52"/>
-      <c r="G26" s="55"/>
-      <c r="H26" s="52"/>
+      <c r="A26" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" s="26"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="25"/>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
@@ -2347,18 +2333,18 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="60" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" s="61" t="s">
-        <v>42</v>
-      </c>
-      <c r="C27" s="56"/>
-      <c r="D27" s="57"/>
-      <c r="E27" s="57"/>
-      <c r="F27" s="56"/>
-      <c r="G27" s="58"/>
-      <c r="H27" s="56"/>
+      <c r="A27" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" s="29"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="31"/>
+      <c r="H27" s="29"/>
     </row>
     <row r="28" spans="1:43" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="29" spans="1:43" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2653,16 +2639,16 @@
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4B2C3C2-98C5-40C9-936C-A0749252C73F}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="191d0fcf-6d89-4c90-807a-10f37b8d7a4c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="9a7dc87b-2be1-4fee-871a-355a79ca984c"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="191d0fcf-6d89-4c90-807a-10f37b8d7a4c"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="9a7dc87b-2be1-4fee-871a-355a79ca984c"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
